--- a/samples/점검결과_예시.xlsx
+++ b/samples/점검결과_예시.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:Q16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,242 +407,314 @@
         <v>판정상태</v>
       </c>
       <c r="C1" t="str">
+        <v>확인필요</v>
+      </c>
+      <c r="D1" t="str">
         <v>수출신고번호</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>모델·규격</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>전략물자판정</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
+        <v>통제번호</v>
+      </c>
+      <c r="H1" t="str">
+        <v>판정구분</v>
+      </c>
+      <c r="I1" t="str">
         <v>도착국</v>
       </c>
-      <c r="G1" t="str">
+      <c r="J1" t="str">
         <v>신고일</v>
       </c>
-      <c r="H1" t="str">
+      <c r="K1" t="str">
         <v>수량</v>
       </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
         <v>결제금액</v>
       </c>
-      <c r="J1" t="str">
+      <c r="M1" t="str">
         <v>통화</v>
       </c>
-      <c r="K1" t="str">
+      <c r="N1" t="str">
         <v>USD환산</v>
       </c>
-      <c r="L1" t="str">
-        <v>USD근거</v>
-      </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
+        <v>적용환율</v>
+      </c>
+      <c r="P1" t="str">
+        <v>허가·면제근거</v>
+      </c>
+      <c r="Q1" t="str">
         <v>근거/메모</v>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="B2" t="str">
-        <v>허가 정상</v>
+        <v>무허가·우려국</v>
       </c>
       <c r="C2" t="str">
-        <v>41234-26-0100011X</v>
+        <v>Y</v>
       </c>
       <c r="D2" t="str">
-        <v>SCM-7200</v>
+        <v>41234-26-0100141X</v>
       </c>
       <c r="E2" t="str">
+        <v>SDR-100</v>
+      </c>
+      <c r="F2" t="str">
         <v>해당</v>
       </c>
-      <c r="F2" t="str">
-        <v>일본</v>
-      </c>
       <c r="G2" t="str">
-        <v>2026-01-12</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1500000</v>
+        <v>5A001</v>
+      </c>
+      <c r="H2" t="str">
+        <v>자가판정</v>
+      </c>
+      <c r="I2" t="str">
+        <v>이란</v>
       </c>
       <c r="J2" t="str">
-        <v>JPY</v>
+        <v>2026-04-25</v>
       </c>
       <c r="K2">
-        <v>10111.11</v>
-      </c>
-      <c r="L2" t="str">
-        <v>JPY9.1원/USD1350원</v>
+        <v>8</v>
+      </c>
+      <c r="L2">
+        <v>9500</v>
       </c>
       <c r="M2" t="str">
-        <v>허가: 일본 / 유효 ~2026-12-31</v>
+        <v>USD</v>
+      </c>
+      <c r="N2">
+        <v>9500</v>
+      </c>
+      <c r="O2" t="str">
+        <v>USD</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v>전략물자 해당·우려국('이란') 수출이나 허가·면제 기록 없음</v>
       </c>
     </row>
     <row r="3">
       <c r="A3">
+        <v>3</v>
+      </c>
+      <c r="B3" t="str">
+        <v>무허가(국가불일치)</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Y</v>
+      </c>
+      <c r="D3" t="str">
+        <v>41234-26-0100031X</v>
+      </c>
+      <c r="E3" t="str">
+        <v>HPA-9000</v>
+      </c>
+      <c r="F3" t="str">
+        <v>해당</v>
+      </c>
+      <c r="G3" t="str">
+        <v>3A001</v>
+      </c>
+      <c r="H3" t="str">
+        <v>전문판정</v>
+      </c>
+      <c r="I3" t="str">
+        <v>중국</v>
+      </c>
+      <c r="J3" t="str">
+        <v>2026-02-03</v>
+      </c>
+      <c r="K3">
         <v>2</v>
       </c>
-      <c r="B3" t="str">
-        <v>면제 정상</v>
-      </c>
-      <c r="C3" t="str">
-        <v>41234-26-0100025X</v>
-      </c>
-      <c r="D3" t="str">
-        <v>SDR-100</v>
-      </c>
-      <c r="E3" t="str">
-        <v>해당</v>
-      </c>
-      <c r="F3" t="str">
-        <v>인도</v>
-      </c>
-      <c r="G3" t="str">
-        <v>2026-01-20</v>
-      </c>
-      <c r="H3">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>45000</v>
-      </c>
-      <c r="J3" t="str">
-        <v>INR</v>
-      </c>
-      <c r="K3">
-        <v>539.8</v>
-      </c>
-      <c r="L3" t="str">
-        <v>INR16.23원/USD1353원</v>
+      <c r="L3">
+        <v>48000</v>
       </c>
       <c r="M3" t="str">
-        <v>허가면제 대상 (USD 539.80)</v>
+        <v>USD</v>
+      </c>
+      <c r="N3">
+        <v>48000</v>
+      </c>
+      <c r="O3" t="str">
+        <v>USD</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v>해당 국가 허가 없음(타 국가 허가만 존재) → 무허가 의심</v>
       </c>
     </row>
     <row r="4">
       <c r="A4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B4" t="str">
-        <v>무허가 의심</v>
+        <v>무허가(국가불일치)</v>
       </c>
       <c r="C4" t="str">
-        <v>41234-26-0100031X</v>
+        <v>Y</v>
       </c>
       <c r="D4" t="str">
-        <v>HPA-9000</v>
+        <v>41234-26-0100094X</v>
       </c>
       <c r="E4" t="str">
+        <v>ENC-55</v>
+      </c>
+      <c r="F4" t="str">
         <v>해당</v>
       </c>
-      <c r="F4" t="str">
-        <v>중국</v>
-      </c>
       <c r="G4" t="str">
-        <v>2026-02-03</v>
-      </c>
-      <c r="H4">
-        <v>2</v>
-      </c>
-      <c r="I4">
-        <v>48000</v>
+        <v>5A002</v>
+      </c>
+      <c r="H4" t="str">
+        <v>전문판정</v>
+      </c>
+      <c r="I4" t="str">
+        <v>미국</v>
       </c>
       <c r="J4" t="str">
-        <v>USD</v>
+        <v>2026-03-22</v>
       </c>
       <c r="K4">
-        <v>48000</v>
-      </c>
-      <c r="L4" t="str">
-        <v>USD</v>
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <v>7000</v>
       </c>
       <c r="M4" t="str">
+        <v>USD</v>
+      </c>
+      <c r="N4">
+        <v>7000</v>
+      </c>
+      <c r="O4" t="str">
+        <v>USD</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
         <v>해당 국가 허가 없음(타 국가 허가만 존재) → 무허가 의심</v>
       </c>
     </row>
     <row r="5">
       <c r="A5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B5" t="str">
-        <v>비전략물자</v>
+        <v>면제 한도초과</v>
       </c>
       <c r="C5" t="str">
-        <v>41234-26-0100042X</v>
+        <v>Y</v>
       </c>
       <c r="D5" t="str">
-        <v>PWC-12</v>
+        <v>41234-26-0100073X</v>
       </c>
       <c r="E5" t="str">
-        <v>비해당</v>
+        <v>SDR-100</v>
       </c>
       <c r="F5" t="str">
-        <v>베트남</v>
+        <v>해당</v>
       </c>
       <c r="G5" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="H5">
-        <v>500</v>
-      </c>
-      <c r="I5">
-        <v>2500</v>
+        <v>5A001</v>
+      </c>
+      <c r="H5" t="str">
+        <v>자가판정</v>
+      </c>
+      <c r="I5" t="str">
+        <v>인도</v>
       </c>
       <c r="J5" t="str">
-        <v>USD</v>
+        <v>2026-03-02</v>
       </c>
       <c r="K5">
-        <v>2500</v>
-      </c>
-      <c r="L5" t="str">
-        <v>USD</v>
+        <v>30</v>
+      </c>
+      <c r="L5">
+        <v>2600000</v>
       </c>
       <c r="M5" t="str">
-        <v>판정: 비해당</v>
+        <v>INR</v>
+      </c>
+      <c r="N5">
+        <v>31184.75</v>
+      </c>
+      <c r="O5" t="str">
+        <v>INR16.36원/USD1364원</v>
+      </c>
+      <c r="P5" t="str">
+        <v>면제: 소액면제</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>면제 한도초과: USD 31184.75 &gt; 한도 1000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="B6" t="str">
-        <v>판정 미실시</v>
+        <v>면제 한도초과</v>
       </c>
       <c r="C6" t="str">
-        <v>41234-26-0100055X</v>
+        <v>Y</v>
       </c>
       <c r="D6" t="str">
-        <v>NEWX-1</v>
+        <v>41234-26-0100120X</v>
       </c>
       <c r="E6" t="str">
-        <v>미등재</v>
+        <v>ENC-55</v>
       </c>
       <c r="F6" t="str">
-        <v>러시아</v>
+        <v>해당</v>
       </c>
       <c r="G6" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="H6">
-        <v>4</v>
-      </c>
-      <c r="I6">
-        <v>8000</v>
+        <v>5A002</v>
+      </c>
+      <c r="H6" t="str">
+        <v>전문판정</v>
+      </c>
+      <c r="I6" t="str">
+        <v>프랑스</v>
       </c>
       <c r="J6" t="str">
+        <v>2026-04-12</v>
+      </c>
+      <c r="K6">
+        <v>2</v>
+      </c>
+      <c r="L6">
+        <v>1400</v>
+      </c>
+      <c r="M6" t="str">
         <v>EUR</v>
       </c>
-      <c r="K6">
-        <v>8652.46</v>
-      </c>
-      <c r="L6" t="str">
-        <v>EUR1472원/USD1361원</v>
-      </c>
-      <c r="M6" t="str">
-        <v>판정DB에 모델 없음 → 무허가 수출은 DB 누락 가능, 별도 판정 필요</v>
+      <c r="N6">
+        <v>1514.12</v>
+      </c>
+      <c r="O6" t="str">
+        <v>EUR1486원/USD1374원</v>
+      </c>
+      <c r="P6" t="str">
+        <v>면제: 소액면제</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>면제 한도초과: USD 1514.12 &gt; 한도 1000</v>
       </c>
     </row>
     <row r="7">
@@ -653,365 +725,473 @@
         <v>허가 기간외</v>
       </c>
       <c r="C7" t="str">
+        <v>Y</v>
+      </c>
+      <c r="D7" t="str">
         <v>41234-27-0100061X</v>
       </c>
-      <c r="D7" t="str">
+      <c r="E7" t="str">
         <v>SCM-7200</v>
       </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
         <v>해당</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
+        <v>2B006</v>
+      </c>
+      <c r="H7" t="str">
+        <v>전문판정</v>
+      </c>
+      <c r="I7" t="str">
         <v>일본</v>
       </c>
-      <c r="G7" t="str">
+      <c r="J7" t="str">
         <v>2027-02-05</v>
       </c>
-      <c r="H7">
+      <c r="K7">
         <v>1</v>
       </c>
-      <c r="I7">
+      <c r="L7">
         <v>1600000</v>
       </c>
-      <c r="J7" t="str">
+      <c r="M7" t="str">
         <v>JPY</v>
       </c>
-      <c r="K7">
+      <c r="N7">
         <v>10789.89</v>
       </c>
-      <c r="L7" t="str">
+      <c r="O7" t="str">
         <v>JPY9.34원/USD1385원</v>
       </c>
-      <c r="M7" t="str">
+      <c r="P7" t="str">
+        <v>허가(만료): P-2025-A11</v>
+      </c>
+      <c r="Q7" t="str">
         <v>해당 국가 허가는 있으나 수출일이 유효기간 밖 (유효 ~2026-12-31)</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B8" t="str">
-        <v>면제 한도초과</v>
+        <v>판정미실시·미등재</v>
       </c>
       <c r="C8" t="str">
-        <v>41234-26-0100073X</v>
+        <v>Y</v>
       </c>
       <c r="D8" t="str">
-        <v>SDR-100</v>
+        <v>41234-26-0100055X</v>
       </c>
       <c r="E8" t="str">
-        <v>해당</v>
+        <v>NEWX-1</v>
       </c>
       <c r="F8" t="str">
-        <v>인도</v>
+        <v>미등재</v>
       </c>
       <c r="G8" t="str">
-        <v>2026-03-02</v>
-      </c>
-      <c r="H8">
-        <v>30</v>
-      </c>
-      <c r="I8">
-        <v>2600000</v>
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>러시아</v>
       </c>
       <c r="J8" t="str">
-        <v>INR</v>
+        <v>2026-02-18</v>
       </c>
       <c r="K8">
-        <v>31184.75</v>
-      </c>
-      <c r="L8" t="str">
-        <v>INR16.36원/USD1364원</v>
+        <v>4</v>
+      </c>
+      <c r="L8">
+        <v>8000</v>
       </c>
       <c r="M8" t="str">
-        <v>면제 한도초과: USD 31184.75 &gt; 한도 1000</v>
+        <v>EUR</v>
+      </c>
+      <c r="N8">
+        <v>8652.46</v>
+      </c>
+      <c r="O8" t="str">
+        <v>EUR1472원/USD1361원</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v>판정DB에 모델 없음 → 무허가 수출은 DB 누락 가능, 별도 판정 필요</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B9" t="str">
         <v>허가 정상</v>
       </c>
       <c r="C9" t="str">
-        <v>41234-26-0100088X</v>
+        <v/>
       </c>
       <c r="D9" t="str">
-        <v>ENC-55</v>
+        <v>41234-26-0100011X</v>
       </c>
       <c r="E9" t="str">
+        <v>SCM-7200</v>
+      </c>
+      <c r="F9" t="str">
         <v>해당</v>
       </c>
-      <c r="F9" t="str">
-        <v>독일</v>
-      </c>
       <c r="G9" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="H9">
-        <v>10</v>
-      </c>
-      <c r="I9">
-        <v>12000</v>
+        <v>2B006</v>
+      </c>
+      <c r="H9" t="str">
+        <v>전문판정</v>
+      </c>
+      <c r="I9" t="str">
+        <v>일본</v>
       </c>
       <c r="J9" t="str">
-        <v>EUR</v>
+        <v>2026-01-12</v>
       </c>
       <c r="K9">
-        <v>12983.89</v>
-      </c>
-      <c r="L9" t="str">
-        <v>EUR1478원/USD1366원</v>
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1500000</v>
       </c>
       <c r="M9" t="str">
-        <v>허가: 독일 / 유효 ~2027-07-31</v>
+        <v>JPY</v>
+      </c>
+      <c r="N9">
+        <v>10111.11</v>
+      </c>
+      <c r="O9" t="str">
+        <v>JPY9.1원/USD1350원</v>
+      </c>
+      <c r="P9" t="str">
+        <v>허가: P-2025-A11</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>허가: 일본 / 유효 ~2026-12-31</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" t="str">
-        <v>무허가 의심</v>
+        <v>허가 정상</v>
       </c>
       <c r="C10" t="str">
-        <v>41234-26-0100094X</v>
+        <v/>
       </c>
       <c r="D10" t="str">
+        <v>41234-26-0100088X</v>
+      </c>
+      <c r="E10" t="str">
         <v>ENC-55</v>
       </c>
-      <c r="E10" t="str">
+      <c r="F10" t="str">
         <v>해당</v>
       </c>
-      <c r="F10" t="str">
-        <v>미국</v>
-      </c>
       <c r="G10" t="str">
-        <v>2026-03-22</v>
-      </c>
-      <c r="H10">
-        <v>5</v>
-      </c>
-      <c r="I10">
-        <v>7000</v>
+        <v>5A002</v>
+      </c>
+      <c r="H10" t="str">
+        <v>전문판정</v>
+      </c>
+      <c r="I10" t="str">
+        <v>독일</v>
       </c>
       <c r="J10" t="str">
-        <v>USD</v>
+        <v>2026-03-15</v>
       </c>
       <c r="K10">
-        <v>7000</v>
-      </c>
-      <c r="L10" t="str">
-        <v>USD</v>
+        <v>10</v>
+      </c>
+      <c r="L10">
+        <v>12000</v>
       </c>
       <c r="M10" t="str">
-        <v>해당 국가 허가 없음(타 국가 허가만 존재) → 무허가 의심</v>
+        <v>EUR</v>
+      </c>
+      <c r="N10">
+        <v>12983.89</v>
+      </c>
+      <c r="O10" t="str">
+        <v>EUR1478원/USD1366원</v>
+      </c>
+      <c r="P10" t="str">
+        <v>허가: P-2025-B07</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>허가: 독일 / 유효 ~2027-07-31</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="str">
-        <v>비전략물자</v>
+        <v>허가 정상</v>
       </c>
       <c r="C11" t="str">
-        <v>41234-26-0100101X</v>
+        <v/>
       </c>
       <c r="D11" t="str">
-        <v>MM-200</v>
+        <v>41234-26-0100112X</v>
       </c>
       <c r="E11" t="str">
-        <v>비해당</v>
+        <v>HPA-9000</v>
       </c>
       <c r="F11" t="str">
-        <v>태국</v>
+        <v>해당</v>
       </c>
       <c r="G11" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="H11">
-        <v>100</v>
-      </c>
-      <c r="I11">
-        <v>3000</v>
+        <v>3A001</v>
+      </c>
+      <c r="H11" t="str">
+        <v>전문판정</v>
+      </c>
+      <c r="I11" t="str">
+        <v>사우디아라비아</v>
       </c>
       <c r="J11" t="str">
-        <v>USD</v>
+        <v>2026-04-05</v>
       </c>
       <c r="K11">
-        <v>3000</v>
-      </c>
-      <c r="L11" t="str">
-        <v>USD</v>
+        <v>1</v>
+      </c>
+      <c r="L11">
+        <v>24000</v>
       </c>
       <c r="M11" t="str">
-        <v>판정: 비해당</v>
+        <v>USD</v>
+      </c>
+      <c r="N11">
+        <v>24000</v>
+      </c>
+      <c r="O11" t="str">
+        <v>USD</v>
+      </c>
+      <c r="P11" t="str">
+        <v>허가: P-2026-C03</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>허가: 사우디아라비아 / 유효 ~2027-01-14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B12" t="str">
         <v>허가 정상</v>
       </c>
       <c r="C12" t="str">
-        <v>41234-26-0100112X</v>
+        <v/>
       </c>
       <c r="D12" t="str">
-        <v>HPA-9000</v>
+        <v>41234-26-0100133X</v>
       </c>
       <c r="E12" t="str">
+        <v>SCM-7200X</v>
+      </c>
+      <c r="F12" t="str">
         <v>해당</v>
       </c>
-      <c r="F12" t="str">
-        <v>사우디아라비아</v>
-      </c>
       <c r="G12" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="H12">
+        <v>2B006</v>
+      </c>
+      <c r="H12" t="str">
+        <v>전문판정</v>
+      </c>
+      <c r="I12" t="str">
+        <v>일본</v>
+      </c>
+      <c r="J12" t="str">
+        <v>2026-04-19</v>
+      </c>
+      <c r="K12">
         <v>1</v>
       </c>
-      <c r="I12">
-        <v>24000</v>
-      </c>
-      <c r="J12" t="str">
-        <v>USD</v>
-      </c>
-      <c r="K12">
-        <v>24000</v>
-      </c>
-      <c r="L12" t="str">
-        <v>USD</v>
+      <c r="L12">
+        <v>1800000</v>
       </c>
       <c r="M12" t="str">
-        <v>허가: 사우디아라비아 / 유효 ~2027-01-14</v>
+        <v>JPY</v>
+      </c>
+      <c r="N12">
+        <v>12130.72</v>
+      </c>
+      <c r="O12" t="str">
+        <v>JPY9.28원/USD1377원</v>
+      </c>
+      <c r="P12" t="str">
+        <v>허가: P-2025-A11</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>허가: 일본 / 유효 ~2026-12-31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B13" t="str">
-        <v>면제 한도초과</v>
+        <v>면제 정상</v>
       </c>
       <c r="C13" t="str">
-        <v>41234-26-0100120X</v>
+        <v/>
       </c>
       <c r="D13" t="str">
-        <v>ENC-55</v>
+        <v>41234-26-0100025X</v>
       </c>
       <c r="E13" t="str">
+        <v>SDR-100</v>
+      </c>
+      <c r="F13" t="str">
         <v>해당</v>
       </c>
-      <c r="F13" t="str">
-        <v>프랑스</v>
-      </c>
       <c r="G13" t="str">
-        <v>2026-04-12</v>
-      </c>
-      <c r="H13">
-        <v>2</v>
-      </c>
-      <c r="I13">
-        <v>1400</v>
+        <v>5A001</v>
+      </c>
+      <c r="H13" t="str">
+        <v>자가판정</v>
+      </c>
+      <c r="I13" t="str">
+        <v>인도</v>
       </c>
       <c r="J13" t="str">
-        <v>EUR</v>
+        <v>2026-01-20</v>
       </c>
       <c r="K13">
-        <v>1514.12</v>
-      </c>
-      <c r="L13" t="str">
-        <v>EUR1486원/USD1374원</v>
+        <v>3</v>
+      </c>
+      <c r="L13">
+        <v>45000</v>
       </c>
       <c r="M13" t="str">
-        <v>면제 한도초과: USD 1514.12 &gt; 한도 1000</v>
+        <v>INR</v>
+      </c>
+      <c r="N13">
+        <v>539.8</v>
+      </c>
+      <c r="O13" t="str">
+        <v>INR16.23원/USD1353원</v>
+      </c>
+      <c r="P13" t="str">
+        <v>면제: 소액면제</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>허가면제 대상 (USD 539.80)</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B14" t="str">
-        <v>허가 정상</v>
+        <v>비전략물자</v>
       </c>
       <c r="C14" t="str">
-        <v>41234-26-0100133X</v>
+        <v/>
       </c>
       <c r="D14" t="str">
-        <v>SCM-7200X</v>
+        <v>41234-26-0100042X</v>
       </c>
       <c r="E14" t="str">
-        <v>해당</v>
+        <v>PWC-12</v>
       </c>
       <c r="F14" t="str">
-        <v>일본</v>
+        <v>비해당</v>
       </c>
       <c r="G14" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14">
-        <v>1800000</v>
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v>자가판정</v>
+      </c>
+      <c r="I14" t="str">
+        <v>베트남</v>
       </c>
       <c r="J14" t="str">
-        <v>JPY</v>
+        <v>2026-02-10</v>
       </c>
       <c r="K14">
-        <v>12130.72</v>
-      </c>
-      <c r="L14" t="str">
-        <v>JPY9.28원/USD1377원</v>
+        <v>500</v>
+      </c>
+      <c r="L14">
+        <v>2500</v>
       </c>
       <c r="M14" t="str">
-        <v>허가: 일본 / 유효 ~2026-12-31</v>
+        <v>USD</v>
+      </c>
+      <c r="N14">
+        <v>2500</v>
+      </c>
+      <c r="O14" t="str">
+        <v>USD</v>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v>판정: 비해당</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B15" t="str">
-        <v>무허가 의심</v>
+        <v>비전략물자</v>
       </c>
       <c r="C15" t="str">
-        <v>41234-26-0100141X</v>
+        <v/>
       </c>
       <c r="D15" t="str">
-        <v>SDR-100</v>
+        <v>41234-26-0100101X</v>
       </c>
       <c r="E15" t="str">
-        <v>해당</v>
+        <v>MM-200</v>
       </c>
       <c r="F15" t="str">
-        <v>이란</v>
+        <v>비해당</v>
       </c>
       <c r="G15" t="str">
-        <v>2026-04-25</v>
-      </c>
-      <c r="H15">
-        <v>8</v>
-      </c>
-      <c r="I15">
-        <v>9500</v>
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v>자가판정</v>
+      </c>
+      <c r="I15" t="str">
+        <v>태국</v>
       </c>
       <c r="J15" t="str">
-        <v>USD</v>
+        <v>2026-03-28</v>
       </c>
       <c r="K15">
-        <v>9500</v>
-      </c>
-      <c r="L15" t="str">
-        <v>USD</v>
+        <v>100</v>
+      </c>
+      <c r="L15">
+        <v>3000</v>
       </c>
       <c r="M15" t="str">
-        <v>전략물자 해당이나 허가·면제 기록 없음</v>
+        <v>USD</v>
+      </c>
+      <c r="N15">
+        <v>3000</v>
+      </c>
+      <c r="O15" t="str">
+        <v>USD</v>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v>판정: 비해당</v>
       </c>
     </row>
     <row r="16">
@@ -1022,42 +1202,54 @@
         <v>비전략물자</v>
       </c>
       <c r="C16" t="str">
+        <v/>
+      </c>
+      <c r="D16" t="str">
         <v>41234-26-0100150X</v>
       </c>
-      <c r="D16" t="str">
+      <c r="E16" t="str">
         <v>BRK-07</v>
       </c>
-      <c r="E16" t="str">
+      <c r="F16" t="str">
         <v>비해당</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v>자가판정</v>
+      </c>
+      <c r="I16" t="str">
         <v>멕시코</v>
       </c>
-      <c r="G16" t="str">
+      <c r="J16" t="str">
         <v>2026-05-02</v>
       </c>
-      <c r="H16">
+      <c r="K16">
         <v>1000</v>
       </c>
-      <c r="I16">
+      <c r="L16">
         <v>1800</v>
       </c>
-      <c r="J16" t="str">
-        <v>USD</v>
-      </c>
-      <c r="K16">
+      <c r="M16" t="str">
+        <v>USD</v>
+      </c>
+      <c r="N16">
         <v>1800</v>
       </c>
-      <c r="L16" t="str">
-        <v>USD</v>
-      </c>
-      <c r="M16" t="str">
+      <c r="O16" t="str">
+        <v>USD</v>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
         <v>판정: 비해당</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/점검결과_예시.xlsx
+++ b/samples/점검결과_예시.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:S19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -407,48 +407,54 @@
         <v>판정상태</v>
       </c>
       <c r="C1" t="str">
+        <v>고위험품목</v>
+      </c>
+      <c r="D1" t="str">
         <v>확인필요</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>수출신고번호</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>모델·규격</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>전략물자판정</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>통제번호</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>판정구분</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>도착국</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>신고일</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>수량</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>결제금액</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>통화</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>USD환산</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>적용환율</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
+        <v>HS부호</v>
+      </c>
+      <c r="R1" t="str">
         <v>허가·면제근거</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>근거/메모</v>
       </c>
     </row>
@@ -460,48 +466,54 @@
         <v>무허가·우려국</v>
       </c>
       <c r="C2" t="str">
+        <v/>
+      </c>
+      <c r="D2" t="str">
         <v>Y</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>41234-26-0100141X</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
         <v>SDR-100</v>
       </c>
-      <c r="F2" t="str">
+      <c r="G2" t="str">
         <v>해당</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <v>5A001</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <v>자가판정</v>
       </c>
-      <c r="I2" t="str">
+      <c r="J2" t="str">
         <v>이란</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>2026-04-25</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>8</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>9500</v>
       </c>
-      <c r="M2" t="str">
-        <v>USD</v>
-      </c>
-      <c r="N2">
+      <c r="N2" t="str">
+        <v>USD</v>
+      </c>
+      <c r="O2">
         <v>9500</v>
       </c>
-      <c r="O2" t="str">
-        <v>USD</v>
-      </c>
       <c r="P2" t="str">
-        <v/>
+        <v>USD</v>
       </c>
       <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
         <v>전략물자 해당·우려국('이란') 수출이나 허가·면제 기록 없음</v>
       </c>
     </row>
@@ -513,48 +525,54 @@
         <v>무허가(국가불일치)</v>
       </c>
       <c r="C3" t="str">
+        <v/>
+      </c>
+      <c r="D3" t="str">
         <v>Y</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>41234-26-0100031X</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
         <v>HPA-9000</v>
       </c>
-      <c r="F3" t="str">
+      <c r="G3" t="str">
         <v>해당</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <v>3A001</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <v>전문판정</v>
       </c>
-      <c r="I3" t="str">
+      <c r="J3" t="str">
         <v>중국</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>2026-02-03</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>2</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>48000</v>
       </c>
-      <c r="M3" t="str">
-        <v>USD</v>
-      </c>
-      <c r="N3">
+      <c r="N3" t="str">
+        <v>USD</v>
+      </c>
+      <c r="O3">
         <v>48000</v>
       </c>
-      <c r="O3" t="str">
-        <v>USD</v>
-      </c>
       <c r="P3" t="str">
-        <v/>
+        <v>USD</v>
       </c>
       <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
         <v>해당 국가 허가 없음(타 국가 허가만 존재) → 무허가 의심</v>
       </c>
     </row>
@@ -566,48 +584,54 @@
         <v>무허가(국가불일치)</v>
       </c>
       <c r="C4" t="str">
+        <v/>
+      </c>
+      <c r="D4" t="str">
         <v>Y</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v>41234-26-0100094X</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
         <v>ENC-55</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>해당</v>
       </c>
-      <c r="G4" t="str">
+      <c r="H4" t="str">
         <v>5A002</v>
       </c>
-      <c r="H4" t="str">
+      <c r="I4" t="str">
         <v>전문판정</v>
       </c>
-      <c r="I4" t="str">
+      <c r="J4" t="str">
         <v>미국</v>
       </c>
-      <c r="J4" t="str">
+      <c r="K4" t="str">
         <v>2026-03-22</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>5</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>7000</v>
       </c>
-      <c r="M4" t="str">
-        <v>USD</v>
-      </c>
-      <c r="N4">
+      <c r="N4" t="str">
+        <v>USD</v>
+      </c>
+      <c r="O4">
         <v>7000</v>
       </c>
-      <c r="O4" t="str">
-        <v>USD</v>
-      </c>
       <c r="P4" t="str">
-        <v/>
+        <v>USD</v>
       </c>
       <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
         <v>해당 국가 허가 없음(타 국가 허가만 존재) → 무허가 의심</v>
       </c>
     </row>
@@ -619,48 +643,54 @@
         <v>면제 한도초과</v>
       </c>
       <c r="C5" t="str">
+        <v/>
+      </c>
+      <c r="D5" t="str">
         <v>Y</v>
       </c>
-      <c r="D5" t="str">
+      <c r="E5" t="str">
         <v>41234-26-0100073X</v>
       </c>
-      <c r="E5" t="str">
+      <c r="F5" t="str">
         <v>SDR-100</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
         <v>해당</v>
       </c>
-      <c r="G5" t="str">
+      <c r="H5" t="str">
         <v>5A001</v>
       </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>자가판정</v>
       </c>
-      <c r="I5" t="str">
+      <c r="J5" t="str">
         <v>인도</v>
       </c>
-      <c r="J5" t="str">
+      <c r="K5" t="str">
         <v>2026-03-02</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>30</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>2600000</v>
       </c>
-      <c r="M5" t="str">
+      <c r="N5" t="str">
         <v>INR</v>
       </c>
-      <c r="N5">
+      <c r="O5">
         <v>31184.75</v>
       </c>
-      <c r="O5" t="str">
+      <c r="P5" t="str">
         <v>INR16.36원/USD1364원</v>
       </c>
-      <c r="P5" t="str">
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
         <v>면제: 소액면제</v>
       </c>
-      <c r="Q5" t="str">
+      <c r="S5" t="str">
         <v>면제 한도초과: USD 31184.75 &gt; 한도 1000</v>
       </c>
     </row>
@@ -672,48 +702,54 @@
         <v>면제 한도초과</v>
       </c>
       <c r="C6" t="str">
+        <v/>
+      </c>
+      <c r="D6" t="str">
         <v>Y</v>
       </c>
-      <c r="D6" t="str">
+      <c r="E6" t="str">
         <v>41234-26-0100120X</v>
       </c>
-      <c r="E6" t="str">
+      <c r="F6" t="str">
         <v>ENC-55</v>
       </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
         <v>해당</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>5A002</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>전문판정</v>
       </c>
-      <c r="I6" t="str">
+      <c r="J6" t="str">
         <v>프랑스</v>
       </c>
-      <c r="J6" t="str">
+      <c r="K6" t="str">
         <v>2026-04-12</v>
       </c>
-      <c r="K6">
+      <c r="L6">
         <v>2</v>
       </c>
-      <c r="L6">
+      <c r="M6">
         <v>1400</v>
       </c>
-      <c r="M6" t="str">
+      <c r="N6" t="str">
         <v>EUR</v>
       </c>
-      <c r="N6">
+      <c r="O6">
         <v>1514.12</v>
       </c>
-      <c r="O6" t="str">
+      <c r="P6" t="str">
         <v>EUR1486원/USD1374원</v>
       </c>
-      <c r="P6" t="str">
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
         <v>면제: 소액면제</v>
       </c>
-      <c r="Q6" t="str">
+      <c r="S6" t="str">
         <v>면제 한도초과: USD 1514.12 &gt; 한도 1000</v>
       </c>
     </row>
@@ -725,213 +761,237 @@
         <v>허가 기간외</v>
       </c>
       <c r="C7" t="str">
+        <v/>
+      </c>
+      <c r="D7" t="str">
         <v>Y</v>
       </c>
-      <c r="D7" t="str">
+      <c r="E7" t="str">
         <v>41234-27-0100061X</v>
       </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
         <v>SCM-7200</v>
       </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
         <v>해당</v>
       </c>
-      <c r="G7" t="str">
+      <c r="H7" t="str">
         <v>2B006</v>
       </c>
-      <c r="H7" t="str">
+      <c r="I7" t="str">
         <v>전문판정</v>
       </c>
-      <c r="I7" t="str">
+      <c r="J7" t="str">
         <v>일본</v>
       </c>
-      <c r="J7" t="str">
+      <c r="K7" t="str">
         <v>2027-02-05</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>1</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>1600000</v>
       </c>
-      <c r="M7" t="str">
+      <c r="N7" t="str">
         <v>JPY</v>
       </c>
-      <c r="N7">
+      <c r="O7">
         <v>10789.89</v>
       </c>
-      <c r="O7" t="str">
+      <c r="P7" t="str">
         <v>JPY9.34원/USD1385원</v>
       </c>
-      <c r="P7" t="str">
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
         <v>허가(만료): P-2025-A11</v>
       </c>
-      <c r="Q7" t="str">
+      <c r="S7" t="str">
         <v>해당 국가 허가는 있으나 수출일이 유효기간 밖 (유효 ~2026-12-31)</v>
       </c>
     </row>
     <row r="8">
       <c r="A8">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="B8" t="str">
         <v>판정미실시·미등재</v>
       </c>
       <c r="C8" t="str">
+        <v>서버(GPU 포함 확인필요) · GPU</v>
+      </c>
+      <c r="D8" t="str">
         <v>Y</v>
       </c>
-      <c r="D8" t="str">
-        <v>41234-26-0100055X</v>
-      </c>
       <c r="E8" t="str">
-        <v>NEWX-1</v>
+        <v>41234-26-0100172X</v>
       </c>
       <c r="F8" t="str">
+        <v>SVR-H100-8U</v>
+      </c>
+      <c r="G8" t="str">
         <v>미등재</v>
       </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
       <c r="H8" t="str">
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>러시아</v>
+        <v/>
       </c>
       <c r="J8" t="str">
-        <v>2026-02-18</v>
-      </c>
-      <c r="K8">
-        <v>4</v>
+        <v>싱가포르</v>
+      </c>
+      <c r="K8" t="str">
+        <v>2026-05-15</v>
       </c>
       <c r="L8">
-        <v>8000</v>
-      </c>
-      <c r="M8" t="str">
-        <v>EUR</v>
-      </c>
-      <c r="N8">
-        <v>8652.46</v>
-      </c>
-      <c r="O8" t="str">
-        <v>EUR1472원/USD1361원</v>
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>520000</v>
+      </c>
+      <c r="N8" t="str">
+        <v>USD</v>
+      </c>
+      <c r="O8">
+        <v>520000</v>
       </c>
       <c r="P8" t="str">
-        <v/>
+        <v>USD</v>
       </c>
       <c r="Q8" t="str">
+        <v>8471499000</v>
+      </c>
+      <c r="R8" t="str">
+        <v/>
+      </c>
+      <c r="S8" t="str">
         <v>판정DB에 모델 없음 → 무허가 수출은 DB 누락 가능, 별도 판정 필요</v>
       </c>
     </row>
     <row r="9">
       <c r="A9">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B9" t="str">
-        <v>허가 정상</v>
+        <v>판정미실시·미등재</v>
       </c>
       <c r="C9" t="str">
-        <v/>
+        <v>기지국(모델코드)</v>
       </c>
       <c r="D9" t="str">
-        <v>41234-26-0100011X</v>
+        <v>Y</v>
       </c>
       <c r="E9" t="str">
-        <v>SCM-7200</v>
+        <v>41234-26-0100183X</v>
       </c>
       <c r="F9" t="str">
-        <v>해당</v>
+        <v>SLS-4400B</v>
       </c>
       <c r="G9" t="str">
-        <v>2B006</v>
+        <v>미등재</v>
       </c>
       <c r="H9" t="str">
-        <v>전문판정</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>일본</v>
+        <v/>
       </c>
       <c r="J9" t="str">
-        <v>2026-01-12</v>
-      </c>
-      <c r="K9">
-        <v>1</v>
+        <v>폴란드</v>
+      </c>
+      <c r="K9" t="str">
+        <v>2026-05-20</v>
       </c>
       <c r="L9">
-        <v>1500000</v>
-      </c>
-      <c r="M9" t="str">
-        <v>JPY</v>
-      </c>
-      <c r="N9">
-        <v>10111.11</v>
-      </c>
-      <c r="O9" t="str">
-        <v>JPY9.1원/USD1350원</v>
+        <v>6</v>
+      </c>
+      <c r="M9">
+        <v>54000</v>
+      </c>
+      <c r="N9" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="O9">
+        <v>58415.34</v>
       </c>
       <c r="P9" t="str">
-        <v>허가: P-2025-A11</v>
+        <v>EUR1495원/USD1382원</v>
       </c>
       <c r="Q9" t="str">
-        <v>허가: 일본 / 유효 ~2026-12-31</v>
+        <v>8517792000</v>
+      </c>
+      <c r="R9" t="str">
+        <v/>
+      </c>
+      <c r="S9" t="str">
+        <v>판정DB에 모델 없음 → 무허가 수출은 DB 누락 가능, 별도 판정 필요</v>
       </c>
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B10" t="str">
-        <v>허가 정상</v>
+        <v>판정미실시·미등재</v>
       </c>
       <c r="C10" t="str">
         <v/>
       </c>
       <c r="D10" t="str">
-        <v>41234-26-0100088X</v>
+        <v>Y</v>
       </c>
       <c r="E10" t="str">
-        <v>ENC-55</v>
+        <v>41234-26-0100055X</v>
       </c>
       <c r="F10" t="str">
-        <v>해당</v>
+        <v>NEWX-1</v>
       </c>
       <c r="G10" t="str">
-        <v>5A002</v>
+        <v>미등재</v>
       </c>
       <c r="H10" t="str">
-        <v>전문판정</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>독일</v>
+        <v/>
       </c>
       <c r="J10" t="str">
-        <v>2026-03-15</v>
-      </c>
-      <c r="K10">
-        <v>10</v>
+        <v>러시아</v>
+      </c>
+      <c r="K10" t="str">
+        <v>2026-02-18</v>
       </c>
       <c r="L10">
-        <v>12000</v>
-      </c>
-      <c r="M10" t="str">
+        <v>4</v>
+      </c>
+      <c r="M10">
+        <v>8000</v>
+      </c>
+      <c r="N10" t="str">
         <v>EUR</v>
       </c>
-      <c r="N10">
-        <v>12983.89</v>
-      </c>
-      <c r="O10" t="str">
-        <v>EUR1478원/USD1366원</v>
+      <c r="O10">
+        <v>8652.46</v>
       </c>
       <c r="P10" t="str">
-        <v>허가: P-2025-B07</v>
+        <v>EUR1472원/USD1361원</v>
       </c>
       <c r="Q10" t="str">
-        <v>허가: 독일 / 유효 ~2027-07-31</v>
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v/>
+      </c>
+      <c r="S10" t="str">
+        <v>판정DB에 모델 없음 → 무허가 수출은 DB 누락 가능, 별도 판정 필요</v>
       </c>
     </row>
     <row r="11">
       <c r="A11">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B11" t="str">
         <v>허가 정상</v>
@@ -940,51 +1000,57 @@
         <v/>
       </c>
       <c r="D11" t="str">
-        <v>41234-26-0100112X</v>
+        <v/>
       </c>
       <c r="E11" t="str">
-        <v>HPA-9000</v>
+        <v>41234-26-0100011X</v>
       </c>
       <c r="F11" t="str">
+        <v>SCM-7200</v>
+      </c>
+      <c r="G11" t="str">
         <v>해당</v>
       </c>
-      <c r="G11" t="str">
-        <v>3A001</v>
-      </c>
       <c r="H11" t="str">
+        <v>2B006</v>
+      </c>
+      <c r="I11" t="str">
         <v>전문판정</v>
       </c>
-      <c r="I11" t="str">
-        <v>사우디아라비아</v>
-      </c>
       <c r="J11" t="str">
-        <v>2026-04-05</v>
-      </c>
-      <c r="K11">
+        <v>일본</v>
+      </c>
+      <c r="K11" t="str">
+        <v>2026-01-12</v>
+      </c>
+      <c r="L11">
         <v>1</v>
       </c>
-      <c r="L11">
-        <v>24000</v>
-      </c>
-      <c r="M11" t="str">
-        <v>USD</v>
-      </c>
-      <c r="N11">
-        <v>24000</v>
-      </c>
-      <c r="O11" t="str">
-        <v>USD</v>
+      <c r="M11">
+        <v>1500000</v>
+      </c>
+      <c r="N11" t="str">
+        <v>JPY</v>
+      </c>
+      <c r="O11">
+        <v>10111.11</v>
       </c>
       <c r="P11" t="str">
-        <v>허가: P-2026-C03</v>
+        <v>JPY9.1원/USD1350원</v>
       </c>
       <c r="Q11" t="str">
-        <v>허가: 사우디아라비아 / 유효 ~2027-01-14</v>
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v>허가: P-2025-A11</v>
+      </c>
+      <c r="S11" t="str">
+        <v>허가: 일본 / 유효 ~2026-12-31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B12" t="str">
         <v>허가 정상</v>
@@ -993,263 +1059,470 @@
         <v/>
       </c>
       <c r="D12" t="str">
-        <v>41234-26-0100133X</v>
+        <v/>
       </c>
       <c r="E12" t="str">
-        <v>SCM-7200X</v>
+        <v>41234-26-0100088X</v>
       </c>
       <c r="F12" t="str">
+        <v>ENC-55</v>
+      </c>
+      <c r="G12" t="str">
         <v>해당</v>
       </c>
-      <c r="G12" t="str">
-        <v>2B006</v>
-      </c>
       <c r="H12" t="str">
+        <v>5A002</v>
+      </c>
+      <c r="I12" t="str">
         <v>전문판정</v>
       </c>
-      <c r="I12" t="str">
-        <v>일본</v>
-      </c>
       <c r="J12" t="str">
-        <v>2026-04-19</v>
-      </c>
-      <c r="K12">
-        <v>1</v>
+        <v>독일</v>
+      </c>
+      <c r="K12" t="str">
+        <v>2026-03-15</v>
       </c>
       <c r="L12">
-        <v>1800000</v>
-      </c>
-      <c r="M12" t="str">
-        <v>JPY</v>
-      </c>
-      <c r="N12">
-        <v>12130.72</v>
-      </c>
-      <c r="O12" t="str">
-        <v>JPY9.28원/USD1377원</v>
+        <v>10</v>
+      </c>
+      <c r="M12">
+        <v>12000</v>
+      </c>
+      <c r="N12" t="str">
+        <v>EUR</v>
+      </c>
+      <c r="O12">
+        <v>12983.89</v>
       </c>
       <c r="P12" t="str">
-        <v>허가: P-2025-A11</v>
+        <v>EUR1478원/USD1366원</v>
       </c>
       <c r="Q12" t="str">
-        <v>허가: 일본 / 유효 ~2026-12-31</v>
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v>허가: P-2025-B07</v>
+      </c>
+      <c r="S12" t="str">
+        <v>허가: 독일 / 유효 ~2027-07-31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B13" t="str">
-        <v>면제 정상</v>
+        <v>허가 정상</v>
       </c>
       <c r="C13" t="str">
         <v/>
       </c>
       <c r="D13" t="str">
-        <v>41234-26-0100025X</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v>SDR-100</v>
+        <v>41234-26-0100112X</v>
       </c>
       <c r="F13" t="str">
+        <v>HPA-9000</v>
+      </c>
+      <c r="G13" t="str">
         <v>해당</v>
       </c>
-      <c r="G13" t="str">
-        <v>5A001</v>
-      </c>
       <c r="H13" t="str">
-        <v>자가판정</v>
+        <v>3A001</v>
       </c>
       <c r="I13" t="str">
-        <v>인도</v>
+        <v>전문판정</v>
       </c>
       <c r="J13" t="str">
-        <v>2026-01-20</v>
-      </c>
-      <c r="K13">
-        <v>3</v>
+        <v>사우디아라비아</v>
+      </c>
+      <c r="K13" t="str">
+        <v>2026-04-05</v>
       </c>
       <c r="L13">
-        <v>45000</v>
-      </c>
-      <c r="M13" t="str">
-        <v>INR</v>
-      </c>
-      <c r="N13">
-        <v>539.8</v>
-      </c>
-      <c r="O13" t="str">
-        <v>INR16.23원/USD1353원</v>
+        <v>1</v>
+      </c>
+      <c r="M13">
+        <v>24000</v>
+      </c>
+      <c r="N13" t="str">
+        <v>USD</v>
+      </c>
+      <c r="O13">
+        <v>24000</v>
       </c>
       <c r="P13" t="str">
-        <v>면제: 소액면제</v>
+        <v>USD</v>
       </c>
       <c r="Q13" t="str">
-        <v>허가면제 대상 (USD 539.80)</v>
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v>허가: P-2026-C03</v>
+      </c>
+      <c r="S13" t="str">
+        <v>허가: 사우디아라비아 / 유효 ~2027-01-14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>비전략물자</v>
+        <v>허가 정상</v>
       </c>
       <c r="C14" t="str">
         <v/>
       </c>
       <c r="D14" t="str">
-        <v>41234-26-0100042X</v>
+        <v/>
       </c>
       <c r="E14" t="str">
-        <v>PWC-12</v>
+        <v>41234-26-0100133X</v>
       </c>
       <c r="F14" t="str">
-        <v>비해당</v>
+        <v>SCM-7200X</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>해당</v>
       </c>
       <c r="H14" t="str">
-        <v>자가판정</v>
+        <v>2B006</v>
       </c>
       <c r="I14" t="str">
-        <v>베트남</v>
+        <v>전문판정</v>
       </c>
       <c r="J14" t="str">
-        <v>2026-02-10</v>
-      </c>
-      <c r="K14">
-        <v>500</v>
+        <v>일본</v>
+      </c>
+      <c r="K14" t="str">
+        <v>2026-04-19</v>
       </c>
       <c r="L14">
-        <v>2500</v>
-      </c>
-      <c r="M14" t="str">
-        <v>USD</v>
-      </c>
-      <c r="N14">
-        <v>2500</v>
-      </c>
-      <c r="O14" t="str">
-        <v>USD</v>
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1800000</v>
+      </c>
+      <c r="N14" t="str">
+        <v>JPY</v>
+      </c>
+      <c r="O14">
+        <v>12130.72</v>
       </c>
       <c r="P14" t="str">
-        <v/>
+        <v>JPY9.28원/USD1377원</v>
       </c>
       <c r="Q14" t="str">
-        <v>판정: 비해당</v>
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v>허가: P-2025-A11</v>
+      </c>
+      <c r="S14" t="str">
+        <v>허가: 일본 / 유효 ~2026-12-31</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B15" t="str">
-        <v>비전략물자</v>
+        <v>면제 정상</v>
       </c>
       <c r="C15" t="str">
         <v/>
       </c>
       <c r="D15" t="str">
-        <v>41234-26-0100101X</v>
+        <v/>
       </c>
       <c r="E15" t="str">
-        <v>MM-200</v>
+        <v>41234-26-0100025X</v>
       </c>
       <c r="F15" t="str">
-        <v>비해당</v>
+        <v>SDR-100</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>해당</v>
       </c>
       <c r="H15" t="str">
+        <v>5A001</v>
+      </c>
+      <c r="I15" t="str">
         <v>자가판정</v>
       </c>
-      <c r="I15" t="str">
-        <v>태국</v>
-      </c>
       <c r="J15" t="str">
-        <v>2026-03-28</v>
-      </c>
-      <c r="K15">
-        <v>100</v>
+        <v>인도</v>
+      </c>
+      <c r="K15" t="str">
+        <v>2026-01-20</v>
       </c>
       <c r="L15">
-        <v>3000</v>
-      </c>
-      <c r="M15" t="str">
-        <v>USD</v>
-      </c>
-      <c r="N15">
-        <v>3000</v>
-      </c>
-      <c r="O15" t="str">
-        <v>USD</v>
+        <v>3</v>
+      </c>
+      <c r="M15">
+        <v>45000</v>
+      </c>
+      <c r="N15" t="str">
+        <v>INR</v>
+      </c>
+      <c r="O15">
+        <v>539.8</v>
       </c>
       <c r="P15" t="str">
-        <v/>
+        <v>INR16.23원/USD1353원</v>
       </c>
       <c r="Q15" t="str">
-        <v>판정: 비해당</v>
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v>면제: 소액면제</v>
+      </c>
+      <c r="S15" t="str">
+        <v>허가면제 대상 (USD 539.80)</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="str">
         <v>비전략물자</v>
       </c>
       <c r="C16" t="str">
-        <v/>
+        <v>공작기계</v>
       </c>
       <c r="D16" t="str">
+        <v>Y</v>
+      </c>
+      <c r="E16" t="str">
+        <v>41234-26-0100161X</v>
+      </c>
+      <c r="F16" t="str">
+        <v>VMC-850</v>
+      </c>
+      <c r="G16" t="str">
+        <v>비해당</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>자가판정</v>
+      </c>
+      <c r="J16" t="str">
+        <v>인도네시아</v>
+      </c>
+      <c r="K16" t="str">
+        <v>2026-05-10</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>85000</v>
+      </c>
+      <c r="N16" t="str">
+        <v>USD</v>
+      </c>
+      <c r="O16">
+        <v>85000</v>
+      </c>
+      <c r="P16" t="str">
+        <v>USD</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>8459610000</v>
+      </c>
+      <c r="R16" t="str">
+        <v/>
+      </c>
+      <c r="S16" t="str">
+        <v>판정: 비해당</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>4</v>
+      </c>
+      <c r="B17" t="str">
+        <v>비전략물자</v>
+      </c>
+      <c r="C17" t="str">
+        <v/>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v>41234-26-0100042X</v>
+      </c>
+      <c r="F17" t="str">
+        <v>PWC-12</v>
+      </c>
+      <c r="G17" t="str">
+        <v>비해당</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>자가판정</v>
+      </c>
+      <c r="J17" t="str">
+        <v>베트남</v>
+      </c>
+      <c r="K17" t="str">
+        <v>2026-02-10</v>
+      </c>
+      <c r="L17">
+        <v>500</v>
+      </c>
+      <c r="M17">
+        <v>2500</v>
+      </c>
+      <c r="N17" t="str">
+        <v>USD</v>
+      </c>
+      <c r="O17">
+        <v>2500</v>
+      </c>
+      <c r="P17" t="str">
+        <v>USD</v>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v/>
+      </c>
+      <c r="S17" t="str">
+        <v>판정: 비해당</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>10</v>
+      </c>
+      <c r="B18" t="str">
+        <v>비전략물자</v>
+      </c>
+      <c r="C18" t="str">
+        <v/>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v>41234-26-0100101X</v>
+      </c>
+      <c r="F18" t="str">
+        <v>MM-200</v>
+      </c>
+      <c r="G18" t="str">
+        <v>비해당</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>자가판정</v>
+      </c>
+      <c r="J18" t="str">
+        <v>태국</v>
+      </c>
+      <c r="K18" t="str">
+        <v>2026-03-28</v>
+      </c>
+      <c r="L18">
+        <v>100</v>
+      </c>
+      <c r="M18">
+        <v>3000</v>
+      </c>
+      <c r="N18" t="str">
+        <v>USD</v>
+      </c>
+      <c r="O18">
+        <v>3000</v>
+      </c>
+      <c r="P18" t="str">
+        <v>USD</v>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v/>
+      </c>
+      <c r="S18" t="str">
+        <v>판정: 비해당</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>15</v>
+      </c>
+      <c r="B19" t="str">
+        <v>비전략물자</v>
+      </c>
+      <c r="C19" t="str">
+        <v/>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
         <v>41234-26-0100150X</v>
       </c>
-      <c r="E16" t="str">
+      <c r="F19" t="str">
         <v>BRK-07</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G19" t="str">
         <v>비해당</v>
       </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
         <v>자가판정</v>
       </c>
-      <c r="I16" t="str">
+      <c r="J19" t="str">
         <v>멕시코</v>
       </c>
-      <c r="J16" t="str">
+      <c r="K19" t="str">
         <v>2026-05-02</v>
       </c>
-      <c r="K16">
+      <c r="L19">
         <v>1000</v>
       </c>
-      <c r="L16">
+      <c r="M19">
         <v>1800</v>
       </c>
-      <c r="M16" t="str">
-        <v>USD</v>
-      </c>
-      <c r="N16">
+      <c r="N19" t="str">
+        <v>USD</v>
+      </c>
+      <c r="O19">
         <v>1800</v>
       </c>
-      <c r="O16" t="str">
-        <v>USD</v>
-      </c>
-      <c r="P16" t="str">
-        <v/>
-      </c>
-      <c r="Q16" t="str">
+      <c r="P19" t="str">
+        <v>USD</v>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v/>
+      </c>
+      <c r="S19" t="str">
         <v>판정: 비해당</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S19"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/점검결과_예시.xlsx
+++ b/samples/점검결과_예시.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -932,22 +932,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B10" t="str">
         <v>판정미실시·미등재</v>
       </c>
       <c r="C10" t="str">
-        <v/>
+        <v>기지국(HS code)</v>
       </c>
       <c r="D10" t="str">
         <v>Y</v>
       </c>
       <c r="E10" t="str">
-        <v>41234-26-0100055X</v>
+        <v>41234-26-0100194X</v>
       </c>
       <c r="F10" t="str">
-        <v>NEWX-1</v>
+        <v>TTM-300</v>
       </c>
       <c r="G10" t="str">
         <v>미등재</v>
@@ -959,28 +959,28 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>러시아</v>
+        <v>브라질</v>
       </c>
       <c r="K10" t="str">
-        <v>2026-02-18</v>
+        <v>2026-05-25</v>
       </c>
       <c r="L10">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M10">
-        <v>8000</v>
+        <v>36000</v>
       </c>
       <c r="N10" t="str">
-        <v>EUR</v>
+        <v>USD</v>
       </c>
       <c r="O10">
-        <v>8652.46</v>
+        <v>36000</v>
       </c>
       <c r="P10" t="str">
-        <v>EUR1472원/USD1361원</v>
+        <v>USD</v>
       </c>
       <c r="Q10" t="str">
-        <v/>
+        <v>8517621000</v>
       </c>
       <c r="R10" t="str">
         <v/>
@@ -991,66 +991,66 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B11" t="str">
-        <v>허가 정상</v>
+        <v>판정미실시·미등재</v>
       </c>
       <c r="C11" t="str">
         <v/>
       </c>
       <c r="D11" t="str">
-        <v/>
+        <v>Y</v>
       </c>
       <c r="E11" t="str">
-        <v>41234-26-0100011X</v>
+        <v>41234-26-0100055X</v>
       </c>
       <c r="F11" t="str">
-        <v>SCM-7200</v>
+        <v>NEWX-1</v>
       </c>
       <c r="G11" t="str">
-        <v>해당</v>
+        <v>미등재</v>
       </c>
       <c r="H11" t="str">
-        <v>2B006</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>전문판정</v>
+        <v/>
       </c>
       <c r="J11" t="str">
-        <v>일본</v>
+        <v>러시아</v>
       </c>
       <c r="K11" t="str">
-        <v>2026-01-12</v>
+        <v>2026-02-18</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M11">
-        <v>1500000</v>
+        <v>8000</v>
       </c>
       <c r="N11" t="str">
-        <v>JPY</v>
+        <v>EUR</v>
       </c>
       <c r="O11">
-        <v>10111.11</v>
+        <v>8652.46</v>
       </c>
       <c r="P11" t="str">
-        <v>JPY9.1원/USD1350원</v>
+        <v>EUR1472원/USD1361원</v>
       </c>
       <c r="Q11" t="str">
         <v/>
       </c>
       <c r="R11" t="str">
-        <v>허가: P-2025-A11</v>
+        <v/>
       </c>
       <c r="S11" t="str">
-        <v>허가: 일본 / 유효 ~2026-12-31</v>
+        <v>판정DB에 모델 없음 → 무허가 수출은 DB 누락 가능, 별도 판정 필요</v>
       </c>
     </row>
     <row r="12">
       <c r="A12">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="B12" t="str">
         <v>허가 정상</v>
@@ -1062,54 +1062,54 @@
         <v/>
       </c>
       <c r="E12" t="str">
-        <v>41234-26-0100088X</v>
+        <v>41234-26-0100011X</v>
       </c>
       <c r="F12" t="str">
-        <v>ENC-55</v>
+        <v>SCM-7200</v>
       </c>
       <c r="G12" t="str">
         <v>해당</v>
       </c>
       <c r="H12" t="str">
-        <v>5A002</v>
+        <v>2B006</v>
       </c>
       <c r="I12" t="str">
         <v>전문판정</v>
       </c>
       <c r="J12" t="str">
-        <v>독일</v>
+        <v>일본</v>
       </c>
       <c r="K12" t="str">
-        <v>2026-03-15</v>
+        <v>2026-01-12</v>
       </c>
       <c r="L12">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M12">
-        <v>12000</v>
+        <v>1500000</v>
       </c>
       <c r="N12" t="str">
-        <v>EUR</v>
+        <v>JPY</v>
       </c>
       <c r="O12">
-        <v>12983.89</v>
+        <v>10111.11</v>
       </c>
       <c r="P12" t="str">
-        <v>EUR1478원/USD1366원</v>
+        <v>JPY9.1원/USD1350원</v>
       </c>
       <c r="Q12" t="str">
         <v/>
       </c>
       <c r="R12" t="str">
-        <v>허가: P-2025-B07</v>
+        <v>허가: P-2025-A11</v>
       </c>
       <c r="S12" t="str">
-        <v>허가: 독일 / 유효 ~2027-07-31</v>
+        <v>허가: 일본 / 유효 ~2026-12-31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B13" t="str">
         <v>허가 정상</v>
@@ -1121,54 +1121,54 @@
         <v/>
       </c>
       <c r="E13" t="str">
-        <v>41234-26-0100112X</v>
+        <v>41234-26-0100088X</v>
       </c>
       <c r="F13" t="str">
-        <v>HPA-9000</v>
+        <v>ENC-55</v>
       </c>
       <c r="G13" t="str">
         <v>해당</v>
       </c>
       <c r="H13" t="str">
-        <v>3A001</v>
+        <v>5A002</v>
       </c>
       <c r="I13" t="str">
         <v>전문판정</v>
       </c>
       <c r="J13" t="str">
-        <v>사우디아라비아</v>
+        <v>독일</v>
       </c>
       <c r="K13" t="str">
-        <v>2026-04-05</v>
+        <v>2026-03-15</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M13">
-        <v>24000</v>
+        <v>12000</v>
       </c>
       <c r="N13" t="str">
-        <v>USD</v>
+        <v>EUR</v>
       </c>
       <c r="O13">
-        <v>24000</v>
+        <v>12983.89</v>
       </c>
       <c r="P13" t="str">
-        <v>USD</v>
+        <v>EUR1478원/USD1366원</v>
       </c>
       <c r="Q13" t="str">
         <v/>
       </c>
       <c r="R13" t="str">
-        <v>허가: P-2026-C03</v>
+        <v>허가: P-2025-B07</v>
       </c>
       <c r="S13" t="str">
-        <v>허가: 사우디아라비아 / 유효 ~2027-01-14</v>
+        <v>허가: 독일 / 유효 ~2027-07-31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B14" t="str">
         <v>허가 정상</v>
@@ -1180,57 +1180,57 @@
         <v/>
       </c>
       <c r="E14" t="str">
-        <v>41234-26-0100133X</v>
+        <v>41234-26-0100112X</v>
       </c>
       <c r="F14" t="str">
-        <v>SCM-7200X</v>
+        <v>HPA-9000</v>
       </c>
       <c r="G14" t="str">
         <v>해당</v>
       </c>
       <c r="H14" t="str">
-        <v>2B006</v>
+        <v>3A001</v>
       </c>
       <c r="I14" t="str">
         <v>전문판정</v>
       </c>
       <c r="J14" t="str">
-        <v>일본</v>
+        <v>사우디아라비아</v>
       </c>
       <c r="K14" t="str">
-        <v>2026-04-19</v>
+        <v>2026-04-05</v>
       </c>
       <c r="L14">
         <v>1</v>
       </c>
       <c r="M14">
-        <v>1800000</v>
+        <v>24000</v>
       </c>
       <c r="N14" t="str">
-        <v>JPY</v>
+        <v>USD</v>
       </c>
       <c r="O14">
-        <v>12130.72</v>
+        <v>24000</v>
       </c>
       <c r="P14" t="str">
-        <v>JPY9.28원/USD1377원</v>
+        <v>USD</v>
       </c>
       <c r="Q14" t="str">
         <v/>
       </c>
       <c r="R14" t="str">
-        <v>허가: P-2025-A11</v>
+        <v>허가: P-2026-C03</v>
       </c>
       <c r="S14" t="str">
-        <v>허가: 일본 / 유효 ~2026-12-31</v>
+        <v>허가: 사우디아라비아 / 유효 ~2027-01-14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B15" t="str">
-        <v>면제 정상</v>
+        <v>허가 정상</v>
       </c>
       <c r="C15" t="str">
         <v/>
@@ -1239,128 +1239,128 @@
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>41234-26-0100025X</v>
+        <v>41234-26-0100133X</v>
       </c>
       <c r="F15" t="str">
-        <v>SDR-100</v>
+        <v>SCM-7200X</v>
       </c>
       <c r="G15" t="str">
         <v>해당</v>
       </c>
       <c r="H15" t="str">
-        <v>5A001</v>
+        <v>2B006</v>
       </c>
       <c r="I15" t="str">
-        <v>자가판정</v>
+        <v>전문판정</v>
       </c>
       <c r="J15" t="str">
-        <v>인도</v>
+        <v>일본</v>
       </c>
       <c r="K15" t="str">
-        <v>2026-01-20</v>
+        <v>2026-04-19</v>
       </c>
       <c r="L15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M15">
-        <v>45000</v>
+        <v>1800000</v>
       </c>
       <c r="N15" t="str">
-        <v>INR</v>
+        <v>JPY</v>
       </c>
       <c r="O15">
-        <v>539.8</v>
+        <v>12130.72</v>
       </c>
       <c r="P15" t="str">
-        <v>INR16.23원/USD1353원</v>
+        <v>JPY9.28원/USD1377원</v>
       </c>
       <c r="Q15" t="str">
         <v/>
       </c>
       <c r="R15" t="str">
-        <v>면제: 소액면제</v>
+        <v>허가: P-2025-A11</v>
       </c>
       <c r="S15" t="str">
-        <v>허가면제 대상 (USD 539.80)</v>
+        <v>허가: 일본 / 유효 ~2026-12-31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B16" t="str">
-        <v>비전략물자</v>
+        <v>면제 정상</v>
       </c>
       <c r="C16" t="str">
-        <v>공작기계</v>
+        <v/>
       </c>
       <c r="D16" t="str">
-        <v>Y</v>
+        <v/>
       </c>
       <c r="E16" t="str">
-        <v>41234-26-0100161X</v>
+        <v>41234-26-0100025X</v>
       </c>
       <c r="F16" t="str">
-        <v>VMC-850</v>
+        <v>SDR-100</v>
       </c>
       <c r="G16" t="str">
-        <v>비해당</v>
+        <v>해당</v>
       </c>
       <c r="H16" t="str">
-        <v/>
+        <v>5A001</v>
       </c>
       <c r="I16" t="str">
         <v>자가판정</v>
       </c>
       <c r="J16" t="str">
-        <v>인도네시아</v>
+        <v>인도</v>
       </c>
       <c r="K16" t="str">
-        <v>2026-05-10</v>
+        <v>2026-01-20</v>
       </c>
       <c r="L16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M16">
-        <v>85000</v>
+        <v>45000</v>
       </c>
       <c r="N16" t="str">
-        <v>USD</v>
+        <v>INR</v>
       </c>
       <c r="O16">
-        <v>85000</v>
+        <v>539.8</v>
       </c>
       <c r="P16" t="str">
-        <v>USD</v>
+        <v>INR16.23원/USD1353원</v>
       </c>
       <c r="Q16" t="str">
-        <v>8459610000</v>
+        <v/>
       </c>
       <c r="R16" t="str">
-        <v/>
+        <v>면제: 소액면제</v>
       </c>
       <c r="S16" t="str">
-        <v>판정: 비해당</v>
+        <v>허가면제 대상 (USD 539.80)</v>
       </c>
     </row>
     <row r="17">
       <c r="A17">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="B17" t="str">
         <v>비전략물자</v>
       </c>
       <c r="C17" t="str">
-        <v/>
+        <v>공작기계</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>Y</v>
       </c>
       <c r="E17" t="str">
-        <v>41234-26-0100042X</v>
+        <v>41234-26-0100161X</v>
       </c>
       <c r="F17" t="str">
-        <v>PWC-12</v>
+        <v>VMC-850</v>
       </c>
       <c r="G17" t="str">
         <v>비해당</v>
@@ -1372,28 +1372,28 @@
         <v>자가판정</v>
       </c>
       <c r="J17" t="str">
-        <v>베트남</v>
+        <v>인도네시아</v>
       </c>
       <c r="K17" t="str">
-        <v>2026-02-10</v>
+        <v>2026-05-10</v>
       </c>
       <c r="L17">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="M17">
-        <v>2500</v>
+        <v>85000</v>
       </c>
       <c r="N17" t="str">
         <v>USD</v>
       </c>
       <c r="O17">
-        <v>2500</v>
+        <v>85000</v>
       </c>
       <c r="P17" t="str">
         <v>USD</v>
       </c>
       <c r="Q17" t="str">
-        <v/>
+        <v>8459610000</v>
       </c>
       <c r="R17" t="str">
         <v/>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B18" t="str">
         <v>비전략물자</v>
@@ -1416,10 +1416,10 @@
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>41234-26-0100101X</v>
+        <v>41234-26-0100042X</v>
       </c>
       <c r="F18" t="str">
-        <v>MM-200</v>
+        <v>PWC-12</v>
       </c>
       <c r="G18" t="str">
         <v>비해당</v>
@@ -1431,22 +1431,22 @@
         <v>자가판정</v>
       </c>
       <c r="J18" t="str">
-        <v>태국</v>
+        <v>베트남</v>
       </c>
       <c r="K18" t="str">
-        <v>2026-03-28</v>
+        <v>2026-02-10</v>
       </c>
       <c r="L18">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="M18">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="N18" t="str">
         <v>USD</v>
       </c>
       <c r="O18">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="P18" t="str">
         <v>USD</v>
@@ -1463,7 +1463,7 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B19" t="str">
         <v>비전략물자</v>
@@ -1475,10 +1475,10 @@
         <v/>
       </c>
       <c r="E19" t="str">
-        <v>41234-26-0100150X</v>
+        <v>41234-26-0100101X</v>
       </c>
       <c r="F19" t="str">
-        <v>BRK-07</v>
+        <v>MM-200</v>
       </c>
       <c r="G19" t="str">
         <v>비해당</v>
@@ -1490,22 +1490,22 @@
         <v>자가판정</v>
       </c>
       <c r="J19" t="str">
-        <v>멕시코</v>
+        <v>태국</v>
       </c>
       <c r="K19" t="str">
-        <v>2026-05-02</v>
+        <v>2026-03-28</v>
       </c>
       <c r="L19">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="M19">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="N19" t="str">
         <v>USD</v>
       </c>
       <c r="O19">
-        <v>1800</v>
+        <v>3000</v>
       </c>
       <c r="P19" t="str">
         <v>USD</v>
@@ -1520,9 +1520,68 @@
         <v>판정: 비해당</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20">
+        <v>15</v>
+      </c>
+      <c r="B20" t="str">
+        <v>비전략물자</v>
+      </c>
+      <c r="C20" t="str">
+        <v/>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v>41234-26-0100150X</v>
+      </c>
+      <c r="F20" t="str">
+        <v>BRK-07</v>
+      </c>
+      <c r="G20" t="str">
+        <v>비해당</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>자가판정</v>
+      </c>
+      <c r="J20" t="str">
+        <v>멕시코</v>
+      </c>
+      <c r="K20" t="str">
+        <v>2026-05-02</v>
+      </c>
+      <c r="L20">
+        <v>1000</v>
+      </c>
+      <c r="M20">
+        <v>1800</v>
+      </c>
+      <c r="N20" t="str">
+        <v>USD</v>
+      </c>
+      <c r="O20">
+        <v>1800</v>
+      </c>
+      <c r="P20" t="str">
+        <v>USD</v>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v/>
+      </c>
+      <c r="S20" t="str">
+        <v>판정: 비해당</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S20"/>
   </ignoredErrors>
 </worksheet>
 </file>